--- a/resource/groundTruths/decision/CF_M04_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M04_ground_truth_decision.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA27CEAA-5248-C64E-95D3-1B8D3597B521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87054BC1-D0C5-2E4C-A2DF-0DCA39F98A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="16560" xr2:uid="{BB3B0AD0-61FB-9141-8733-A27066D72F37}"/>
   </bookViews>
@@ -58,30 +58,6 @@
     <t>CF_M04</t>
   </si>
   <si>
-    <t>CF_M04_AD1</t>
-  </si>
-  <si>
-    <t>CF_M04_AD2</t>
-  </si>
-  <si>
-    <t>CF_M04_AD3</t>
-  </si>
-  <si>
-    <t>CF_M04_AD4</t>
-  </si>
-  <si>
-    <t>CF_M04_AD5</t>
-  </si>
-  <si>
-    <t>CF_M04_AD6</t>
-  </si>
-  <si>
-    <t>CF_M04_AD7</t>
-  </si>
-  <si>
-    <t>CF_M04_AD8</t>
-  </si>
-  <si>
     <t>This solution allows you to clearly define relationships between entities and guarantee data integrity, as well as facilitate the evolution of the schema through migrations.</t>
   </si>
   <si>
@@ -137,9 +113,6 @@
     <t>CF_M04_AU01, CF_M04_AU18</t>
   </si>
   <si>
-    <t>CF_M04_AD9</t>
-  </si>
-  <si>
     <t>Both blocks are located in independent repositories, which allows for a decoupled evolution of each part of the system.</t>
   </si>
   <si>
@@ -209,50 +182,77 @@
     <t>This flow ensures complete decoupling between layers, avoiding direct dependencies between the interface and implementation details.</t>
   </si>
   <si>
-    <t>CF_M06_C06</t>
-  </si>
-  <si>
-    <t>CF_M06_C10</t>
-  </si>
-  <si>
-    <t>CF_M06_C11</t>
-  </si>
-  <si>
-    <t>CF_M06_C12</t>
-  </si>
-  <si>
-    <t>CF_M06_C13</t>
-  </si>
-  <si>
-    <t>CF_M06_C15</t>
-  </si>
-  <si>
-    <t>CF_M06_C07, CF_M06_C08</t>
-  </si>
-  <si>
-    <t>CF_M06_C05, CF_M06_C08, C09</t>
-  </si>
-  <si>
-    <t>CF_M06_C05, CF_M06_C08</t>
-  </si>
-  <si>
-    <t>CF_M06_C08, CF_M06_C10</t>
-  </si>
-  <si>
-    <t>CF_M06_C05, CF_M06_C12</t>
-  </si>
-  <si>
-    <t>CF_M06_C14, CF_M06_C08</t>
-  </si>
-  <si>
     <t>CF_M06_R03, CF_M06_R04, CF_M06_R05, CF_M06_C04</t>
+  </si>
+  <si>
+    <t>CF_M04_AD01</t>
+  </si>
+  <si>
+    <t>CF_M04_AD02</t>
+  </si>
+  <si>
+    <t>CF_M04_AD03</t>
+  </si>
+  <si>
+    <t>CF_M04_AD04</t>
+  </si>
+  <si>
+    <t>CF_M04_AD05</t>
+  </si>
+  <si>
+    <t>CF_M04_AD06</t>
+  </si>
+  <si>
+    <t>CF_M04_AD07</t>
+  </si>
+  <si>
+    <t>CF_M04_AD08</t>
+  </si>
+  <si>
+    <t>CF_M04_AD09</t>
+  </si>
+  <si>
+    <t>*CF_M06_C06</t>
+  </si>
+  <si>
+    <t>*CF_M06_C07, *CF_M06_C08</t>
+  </si>
+  <si>
+    <t>CF_M06_C05, *CF_M06_C08, *CF_M06_C09</t>
+  </si>
+  <si>
+    <t>*CF_M06_C08, *CF_M06_C10</t>
+  </si>
+  <si>
+    <t>*CF_M06_C11</t>
+  </si>
+  <si>
+    <t>CF_M06_C05, *CF_M06_C12</t>
+  </si>
+  <si>
+    <t>*CF_M06_C13</t>
+  </si>
+  <si>
+    <t>*CF_M06_C10</t>
+  </si>
+  <si>
+    <t>*CF_M06_C14, *CF_M06_C08</t>
+  </si>
+  <si>
+    <t>*CF_M06_C12</t>
+  </si>
+  <si>
+    <t>*CF_M06_C15</t>
+  </si>
+  <si>
+    <t>CF_M06_C05, *CF_M06_C08</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -274,6 +274,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -659,16 +666,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
       </c>
       <c r="F2">
         <v>55</v>
@@ -679,16 +686,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>56</v>
@@ -699,16 +706,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>56</v>
@@ -719,16 +726,16 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5">
         <v>62</v>
@@ -739,16 +746,16 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>63</v>
@@ -759,16 +766,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>64</v>
@@ -779,16 +786,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F8">
         <v>64</v>
@@ -799,16 +806,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>67</v>
@@ -819,16 +826,16 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F10">
         <v>68</v>
@@ -839,16 +846,16 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -859,16 +866,16 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F12">
         <v>70</v>
@@ -879,16 +886,16 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F13">
         <v>71</v>
@@ -899,16 +906,16 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F14">
         <v>72</v>
@@ -919,16 +926,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F15">
         <v>73</v>
@@ -939,16 +946,16 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F16">
         <v>73</v>
@@ -959,16 +966,16 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F17">
         <v>73</v>
@@ -979,16 +986,16 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F18">
         <v>75</v>
@@ -999,22 +1006,23 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F19">
         <v>84</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/resource/groundTruths/decision/CF_M04_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M04_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87054BC1-D0C5-2E4C-A2DF-0DCA39F98A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474D4B29-D0DA-B040-A4ED-757F242A4AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="16560" xr2:uid="{BB3B0AD0-61FB-9141-8733-A27066D72F37}"/>
+    <workbookView xWindow="7120" yWindow="1040" windowWidth="14480" windowHeight="16560" xr2:uid="{BB3B0AD0-61FB-9141-8733-A27066D72F37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="78">
   <si>
     <t>Document ID</t>
   </si>
@@ -43,9 +43,6 @@
     <t>AD ID</t>
   </si>
   <si>
-    <t>Architectural Element</t>
-  </si>
-  <si>
     <t>AD Source</t>
   </si>
   <si>
@@ -88,164 +85,193 @@
     <t>This communication is based on a unidirectional flow, which improves the predictability of the application's behavior and reduces side effects.</t>
   </si>
   <si>
-    <t xml:space="preserve">Benefits of the approach adopted: The combined use of an architecture
-based on features and the Block/Cubit pattern provides several advantages:
+    <t>The back-end of the project follows the Hexagonal Architecture pattern, which allows the business logic to be completely decoupled from the framework used.</t>
+  </si>
+  <si>
+    <t>CF_M04_P01</t>
+  </si>
+  <si>
+    <t>This functionality allows non-administrator users to access the application without the need for a password, strengthening security and simplifying the login process.</t>
+  </si>
+  <si>
+    <t>CF_M04_AU18</t>
+  </si>
+  <si>
+    <t>This diagram clearly shows the decoupling between the front-end and the authentication service</t>
+  </si>
+  <si>
+    <t>CF_M04_AU01, CF_M04_AU18</t>
+  </si>
+  <si>
+    <t>Both blocks are located in independent repositories, which allows for a decoupled evolution of each part of the system.</t>
+  </si>
+  <si>
+    <t>CF_M04_P05</t>
+  </si>
+  <si>
+    <t>CF_M04_AD10</t>
+  </si>
+  <si>
+    <t>This separation facilitates system maintenance, allows work to be done in parallel and reduces the impact of changes in one part on the other.</t>
+  </si>
+  <si>
+    <t>This structure allows a high degree of modularity, facilitates code reading and improves its scalability.</t>
+  </si>
+  <si>
+    <t>CF_M04_AD11</t>
+  </si>
+  <si>
+    <t>CF_M04_AD12</t>
+  </si>
+  <si>
+    <t>CF_M04_AD13</t>
+  </si>
+  <si>
+    <t>CF_M04_AD14</t>
+  </si>
+  <si>
+    <t>CF_M04_P08</t>
+  </si>
+  <si>
+    <t>This structure ensures that the business logic is independent of the framework and facilitates its evolution and testability.</t>
+  </si>
+  <si>
+    <t>These libraries have been selected after an analysis process to guarantee compatibility, active maintenance and suitability to the needs of the project.</t>
+  </si>
+  <si>
+    <t>CF_M04_AU03</t>
+  </si>
+  <si>
+    <t>These decisions have been key to guaranteeing the quality and sustainability of the project.</t>
+  </si>
+  <si>
+    <t>CF_M04_P01, CF_M04_P04, CF_M04_P08</t>
+  </si>
+  <si>
+    <t>CF_M04_AD15</t>
+  </si>
+  <si>
+    <t>CF_M04_AD16</t>
+  </si>
+  <si>
+    <t>The resulting code is highly maintainable and scalable, as any new functionality or change in the authentication flow only requires the definition of new state and its management in this BlocConsumer.</t>
+  </si>
+  <si>
+    <t>CF_M04_AD17</t>
+  </si>
+  <si>
+    <t>The integration of these services is carried out exclusively from the backend, maintaining the front-end completely decoupled from implementation details.</t>
+  </si>
+  <si>
+    <t>CF_M04_AU04</t>
+  </si>
+  <si>
+    <t>CF_M04_AD18</t>
+  </si>
+  <si>
+    <t>This flow ensures complete decoupling between layers, avoiding direct dependencies between the interface and implementation details.</t>
+  </si>
+  <si>
+    <t>CF_M04_AD01</t>
+  </si>
+  <si>
+    <t>CF_M04_AD02</t>
+  </si>
+  <si>
+    <t>CF_M04_AD03</t>
+  </si>
+  <si>
+    <t>CF_M04_AD04</t>
+  </si>
+  <si>
+    <t>CF_M04_AD05</t>
+  </si>
+  <si>
+    <t>CF_M04_AD06</t>
+  </si>
+  <si>
+    <t>CF_M04_AD07</t>
+  </si>
+  <si>
+    <t>CF_M04_AD08</t>
+  </si>
+  <si>
+    <t>CF_M04_AD09</t>
+  </si>
+  <si>
+    <t>*CF_M04_C06</t>
+  </si>
+  <si>
+    <t>*CF_M04_C07, *CF_M04_C08</t>
+  </si>
+  <si>
+    <t>CF_M04_C05, *CF_M04_C08, *CF_M04_C09</t>
+  </si>
+  <si>
+    <t>*CF_M04_C08, *CF_M04_C10</t>
+  </si>
+  <si>
+    <t>*CF_M04_C11</t>
+  </si>
+  <si>
+    <t>CF_M04_C05, *CF_M04_C12</t>
+  </si>
+  <si>
+    <t>*CF_M04_C13</t>
+  </si>
+  <si>
+    <t>CF_M04_R03, CF_M04_R04, CF_M04_R05, CF_M04_C04</t>
+  </si>
+  <si>
+    <t>*CF_M04_C10</t>
+  </si>
+  <si>
+    <t>*CF_M04_C14, *CF_M04_C08</t>
+  </si>
+  <si>
+    <t>*CF_M04_C12</t>
+  </si>
+  <si>
+    <t>*CF_M04_C15</t>
+  </si>
+  <si>
+    <t>CF_M04_C05, *CF_M04_C08</t>
+  </si>
+  <si>
+    <t>Architectural Element ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benefits of the approach adopted: The combined use of an architecture based on features and the Block/Cubit pattern provides several advantages:
 • Improved code maintainability [...]
 • Better testability of application logic
 </t>
   </si>
   <si>
-    <t>The back-end of the project follows the Hexagonal Architecture pattern, which allows the business logic to be completely decoupled from the framework used.</t>
-  </si>
-  <si>
-    <t>CF_M04_P01</t>
-  </si>
-  <si>
-    <t>This functionality allows non-administrator users to access the application without the need for a password, strengthening security and simplifying the login process.</t>
-  </si>
-  <si>
-    <t>CF_M04_AU18</t>
-  </si>
-  <si>
-    <t>This diagram clearly shows the decoupling between the front-end and the authentication service</t>
-  </si>
-  <si>
-    <t>CF_M04_AU01, CF_M04_AU18</t>
-  </si>
-  <si>
-    <t>Both blocks are located in independent repositories, which allows for a decoupled evolution of each part of the system.</t>
-  </si>
-  <si>
-    <t>CF_M04_P05</t>
-  </si>
-  <si>
-    <t>CF_M04_AD10</t>
-  </si>
-  <si>
-    <t>This separation facilitates system maintenance, allows work to be done in parallel and reduces the impact of changes in one part on the other.</t>
-  </si>
-  <si>
-    <t>This structure allows a high degree of modularity, facilitates code reading and improves its scalability.</t>
-  </si>
-  <si>
-    <t>CF_M04_AD11</t>
-  </si>
-  <si>
-    <t>CF_M04_AD12</t>
-  </si>
-  <si>
-    <t>CF_M04_AD13</t>
-  </si>
-  <si>
-    <t>CF_M04_AD14</t>
-  </si>
-  <si>
-    <t>CF_M04_P08</t>
-  </si>
-  <si>
-    <t>This structure ensures that the business logic is independent of the framework and facilitates its evolution and testability.</t>
-  </si>
-  <si>
-    <t>These libraries have been selected after an analysis process to guarantee compatibility, active maintenance and suitability to the needs of the project.</t>
-  </si>
-  <si>
-    <t>CF_M04_AU03</t>
-  </si>
-  <si>
-    <t>These decisions have been key to guaranteeing the quality and sustainability of the project.</t>
-  </si>
-  <si>
-    <t>CF_M04_P01, CF_M04_P04, CF_M04_P08</t>
-  </si>
-  <si>
-    <t>CF_M04_AD15</t>
-  </si>
-  <si>
-    <t>CF_M04_AD16</t>
-  </si>
-  <si>
-    <t>The resulting code is highly maintainable and scalable, as any new functionality or change in the authentication flow only requires the definition of new state and its management in this BlocConsumer.</t>
-  </si>
-  <si>
-    <t>CF_M04_AD17</t>
-  </si>
-  <si>
-    <t>The integration of these services is carried out exclusively from the backend, maintaining the front-end completely decoupled from implementation details.</t>
-  </si>
-  <si>
-    <t>CF_M04_AU04</t>
-  </si>
-  <si>
-    <t>CF_M04_AD18</t>
-  </si>
-  <si>
-    <t>This flow ensures complete decoupling between layers, avoiding direct dependencies between the interface and implementation details.</t>
-  </si>
-  <si>
-    <t>CF_M06_R03, CF_M06_R04, CF_M06_R05, CF_M06_C04</t>
-  </si>
-  <si>
-    <t>CF_M04_AD01</t>
-  </si>
-  <si>
-    <t>CF_M04_AD02</t>
-  </si>
-  <si>
-    <t>CF_M04_AD03</t>
-  </si>
-  <si>
-    <t>CF_M04_AD04</t>
-  </si>
-  <si>
-    <t>CF_M04_AD05</t>
-  </si>
-  <si>
-    <t>CF_M04_AD06</t>
-  </si>
-  <si>
-    <t>CF_M04_AD07</t>
-  </si>
-  <si>
-    <t>CF_M04_AD08</t>
-  </si>
-  <si>
-    <t>CF_M04_AD09</t>
-  </si>
-  <si>
-    <t>*CF_M06_C06</t>
-  </si>
-  <si>
-    <t>*CF_M06_C07, *CF_M06_C08</t>
-  </si>
-  <si>
-    <t>CF_M06_C05, *CF_M06_C08, *CF_M06_C09</t>
-  </si>
-  <si>
-    <t>*CF_M06_C08, *CF_M06_C10</t>
-  </si>
-  <si>
-    <t>*CF_M06_C11</t>
-  </si>
-  <si>
-    <t>CF_M06_C05, *CF_M06_C12</t>
-  </si>
-  <si>
-    <t>*CF_M06_C13</t>
-  </si>
-  <si>
-    <t>*CF_M06_C10</t>
-  </si>
-  <si>
-    <t>*CF_M06_C14, *CF_M06_C08</t>
-  </si>
-  <si>
-    <t>*CF_M06_C12</t>
-  </si>
-  <si>
-    <t>*CF_M06_C15</t>
-  </si>
-  <si>
-    <t>CF_M06_C05, *CF_M06_C08</t>
+    <t>Flutter (Dart), used for cross-platform development of the mobile app for Android and iOS.</t>
+  </si>
+  <si>
+    <t>*CF_M04_C07</t>
+  </si>
+  <si>
+    <t>CF_M04_AD19</t>
+  </si>
+  <si>
+    <t>CF_M04_AD20</t>
+  </si>
+  <si>
+    <t>CF_M04_AD21</t>
+  </si>
+  <si>
+    <t>This mechanism guarantees technological independence between both parties and allows the system can be consumed, if necessary, by other customers in the future.</t>
+  </si>
+  <si>
+    <t>CF_M04_AU06</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Isolates access to data and simplifies the use of the ORM in cases of use.</t>
+  </si>
+  <si>
+    <t>CF_M04_C05</t>
   </si>
 </sst>
 </file>
@@ -638,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41C44208-F115-994D-8A61-9B0187D7282A}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -649,33 +675,33 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
       <c r="F2">
         <v>55</v>
@@ -683,19 +709,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>56</v>
@@ -703,19 +729,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>56</v>
@@ -723,19 +749,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>62</v>
@@ -743,19 +769,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
       </c>
       <c r="F6">
         <v>63</v>
@@ -763,19 +789,19 @@
     </row>
     <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F7">
         <v>64</v>
@@ -783,19 +809,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8">
         <v>64</v>
@@ -803,19 +829,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F9">
         <v>67</v>
@@ -823,19 +849,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>68</v>
@@ -843,19 +869,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -863,19 +889,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s">
         <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
       </c>
       <c r="F12">
         <v>70</v>
@@ -883,19 +909,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F13">
         <v>71</v>
@@ -903,19 +929,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F14">
         <v>72</v>
@@ -923,19 +949,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F15">
         <v>73</v>
@@ -943,19 +969,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F16">
         <v>73</v>
@@ -963,19 +989,19 @@
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F17">
         <v>73</v>
@@ -983,19 +1009,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F18">
         <v>75</v>
@@ -1003,22 +1029,82 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F19">
         <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
